--- a/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R74-ModeFixationTarifaire/FHIR/TRE-R74-ModeFixationTarifaire?vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/VS-TRE-R74-ModeFixationTarifaire</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -689,7 +689,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.19140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.71875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
